--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,23 +786,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1576,7 +1559,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1632,37 +1615,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1679,7 +1666,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1696,41 +1683,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1747,7 +1734,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1764,7 +1751,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1781,7 +1768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1798,41 +1785,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1849,7 +1836,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1866,7 +1853,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1883,7 +1870,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1900,7 +1887,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1917,7 +1904,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1934,7 +1921,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1951,7 +1938,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1968,7 +1955,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1985,7 +1972,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2002,7 +1989,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2006,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2036,7 +2023,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2053,7 +2040,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2070,7 +2057,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2087,7 +2074,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2104,7 +2091,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2121,7 +2108,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2138,7 +2125,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2155,7 +2142,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2172,7 +2159,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2189,7 +2176,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2206,12 +2193,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2223,12 +2210,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2240,7 +2227,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2257,7 +2244,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2274,7 +2261,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2291,7 +2278,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2308,41 +2295,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2359,7 +2346,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2376,7 +2363,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2393,7 +2380,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2410,12 +2397,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2427,12 +2414,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2444,7 +2431,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2461,7 +2448,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2470,40 +2457,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1559,7 +1576,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1615,41 +1632,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1666,7 +1679,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1683,41 +1696,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1734,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1751,7 +1764,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1768,7 +1781,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1785,41 +1798,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1836,7 +1849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1853,7 +1866,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1870,7 +1883,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1887,7 +1900,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1904,7 +1917,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1921,7 +1934,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1938,7 +1951,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1955,7 +1968,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1972,7 +1985,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1989,7 +2002,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2006,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2023,7 +2036,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2040,7 +2053,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2057,7 +2070,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2074,7 +2087,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,7 +2104,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2108,7 +2121,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2125,7 +2138,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2142,7 +2155,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2159,7 +2172,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2176,7 +2189,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2193,12 +2206,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2210,12 +2223,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2227,7 +2240,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2244,7 +2257,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2261,7 +2274,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2278,7 +2291,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2295,41 +2308,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2346,7 +2359,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2363,7 +2376,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2380,7 +2393,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2397,12 +2410,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2414,12 +2427,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2431,7 +2444,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2448,15 +2461,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1559,7 +1576,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1615,24 +1632,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1649,7 +1664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1666,7 +1681,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1683,24 +1698,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1717,7 +1732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1734,7 +1749,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1751,7 +1766,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1768,7 +1783,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1785,24 +1800,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1819,7 +1834,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1836,7 +1851,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1853,7 +1868,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1870,7 +1885,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1887,7 +1902,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1904,7 +1919,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1921,7 +1936,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1938,7 +1953,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1955,7 +1970,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1972,7 +1987,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1989,7 +2004,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2006,7 +2021,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2023,7 +2038,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2040,7 +2055,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2057,7 +2072,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2074,7 +2089,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2091,7 +2106,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2108,7 +2123,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2125,7 +2140,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2142,7 +2157,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2159,7 +2174,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2176,7 +2191,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2193,12 +2208,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2210,7 +2225,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2227,7 +2242,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2244,7 +2259,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2261,7 +2276,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2278,7 +2293,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2295,24 +2310,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2329,7 +2344,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2346,7 +2361,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2363,7 +2378,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2380,7 +2395,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2397,12 +2412,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2414,7 +2429,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2431,7 +2446,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2448,15 +2463,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1647,24 +1647,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1681,7 +1679,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1698,7 +1696,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1715,24 +1713,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1749,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1766,7 +1764,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1783,7 +1781,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1800,7 +1798,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1817,24 +1815,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1851,7 +1849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1868,7 +1866,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1885,7 +1883,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1902,7 +1900,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1919,7 +1917,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1936,7 +1934,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1953,7 +1951,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1970,7 +1968,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1987,7 +1985,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2004,7 +2002,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2021,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2038,7 +2036,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2055,7 +2053,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2072,7 +2070,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2089,7 +2087,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2106,7 +2104,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2123,7 +2121,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2140,7 +2138,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2157,7 +2155,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2174,7 +2172,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,7 +2189,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2208,7 +2206,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2225,12 +2223,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2242,7 +2240,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2259,7 +2257,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2276,7 +2274,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2293,7 +2291,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2310,7 +2308,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2327,24 +2325,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2361,7 +2359,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2378,7 +2376,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2395,7 +2393,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2412,7 +2410,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2429,12 +2427,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2446,7 +2444,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2463,7 +2461,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2480,17 +2478,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -605,24 +605,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -656,24 +656,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -690,24 +690,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -724,41 +724,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -775,32 +775,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1539,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1551,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1583,6 +1571,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1598,6 +1589,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1613,6 +1607,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1628,6 +1625,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1643,6 +1643,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1658,28 +1661,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1691,12 +1697,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1708,12 +1717,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1725,29 +1737,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1759,12 +1777,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1776,12 +1797,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1793,12 +1817,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1810,12 +1837,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1827,29 +1857,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1861,12 +1897,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1878,12 +1917,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1895,12 +1937,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1912,12 +1957,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1929,12 +1977,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1946,12 +1997,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1963,12 +2017,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1980,12 +2037,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1997,12 +2057,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2014,12 +2077,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2031,12 +2097,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2048,12 +2117,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2065,12 +2137,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2082,12 +2157,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2099,12 +2177,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2116,12 +2197,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2133,12 +2217,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2150,12 +2237,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2167,12 +2257,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,12 +2277,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2201,12 +2297,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2218,12 +2317,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2235,29 +2337,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2269,12 +2377,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2286,12 +2397,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2303,12 +2417,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2320,12 +2437,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2337,29 +2457,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2371,12 +2497,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2388,12 +2517,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2405,12 +2537,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2422,12 +2557,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2439,29 +2577,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2473,12 +2617,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2490,12 +2637,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2507,32 +2657,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2541,18 +2694,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2561,18 +2717,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2581,32 +2740,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Ratio/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Ratio/France.xlsx
@@ -800,33 +800,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ymax (kgN/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -848,6 +853,9 @@
       <c r="E2" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="F2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -867,6 +875,9 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
+      <c r="F3" t="n">
+        <v>0.076</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -886,6 +897,9 @@
       <c r="E4" t="n">
         <v>0.97</v>
       </c>
+      <c r="F4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -905,11 +919,14 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
+      <c r="F5" t="n">
+        <v>0.055</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -924,6 +941,9 @@
       <c r="E6" t="n">
         <v>0.93</v>
       </c>
+      <c r="F6" t="n">
+        <v>0.07199999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -943,6 +963,9 @@
       <c r="E7" t="n">
         <v>0.96</v>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -962,296 +985,344 @@
       <c r="E8" t="n">
         <v>0.99</v>
       </c>
+      <c r="F8" t="n">
+        <v>0.073</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8.494545271436346</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1258.028695776595</v>
+        <v>298.0352137065566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.494545271436346</v>
+        <v>3.725358950618109</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>298.0352137065566</v>
+        <v>93.91634187469002</v>
       </c>
       <c r="E10" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.725358950618109</v>
+        <v>0.4284678107259858</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>93.91634187469002</v>
+        <v>798.4227519871636</v>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4284678107259858</v>
+        <v>0.1147760337501906</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>798.4227519871636</v>
+        <v>741.4878741482962</v>
       </c>
       <c r="E12" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1147760337501906</v>
+        <v>0.4234276777025442</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>741.4878741482962</v>
+        <v>653.5958808184548</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4234276777025442</v>
+        <v>0.7890350849691262</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>653.5958808184548</v>
+        <v>708.5328513558654</v>
       </c>
       <c r="E14" t="n">
         <v>0.98</v>
       </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7890350849691262</v>
+        <v>0.0297040126729066</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>708.5328513558654</v>
+        <v>479.0665488120418</v>
       </c>
       <c r="E15" t="n">
         <v>0.98</v>
       </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0297040126729066</v>
+        <v>2.300538206533874</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>479.0665488120418</v>
+        <v>720.8702528791556</v>
       </c>
       <c r="E16" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.300538206533874</v>
+        <v>0.9480987449948051</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>720.8702528791556</v>
+        <v>196.2491546117922</v>
       </c>
       <c r="E17" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9480987449948051</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>196.2491546117922</v>
+        <v>232.4469112168015</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.1299868387940301</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>232.4469112168015</v>
+        <v>140.0460653151931</v>
       </c>
       <c r="E19" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1299868387940301</v>
+        <v>0.02795804730940496</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>140.0460653151931</v>
+        <v>555.7614057343892</v>
       </c>
       <c r="E20" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02795804730940496</v>
+        <v>0.117623821915902</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>555.7614057343892</v>
+        <v>306.285854730814</v>
       </c>
       <c r="E21" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.117623821915902</v>
+        <v>0.11765772415597</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>306.285854730814</v>
+        <v>4855.568698976085</v>
       </c>
       <c r="E22" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.11765772415597</v>
+        <v>0</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4855.568698976085</v>
+        <v>76.11379959700224</v>
       </c>
       <c r="E23" t="n">
-        <v>0.99</v>
+        <v>0.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1261,16 +1332,19 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>76.11379959700224</v>
+        <v>108.5522120402204</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1280,16 +1354,19 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>108.5522120402204</v>
+        <v>60.90944197572986</v>
       </c>
       <c r="E25" t="n">
-        <v>0.77</v>
+        <v>-0.35</v>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1299,16 +1376,19 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>60.90944197572986</v>
+        <v>48.75594550519521</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.35</v>
+        <v>-0.22</v>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1318,197 +1398,208 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>48.75594550519521</v>
+        <v>39.63340650933579</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.22</v>
+        <v>-0.29</v>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.09402786282857881</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>39.63340650933579</v>
+        <v>18.75680493874448</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.29</v>
+        <v>-0.06</v>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09402786282857881</v>
+        <v>0</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>18.75680493874448</v>
+        <v>22.77702422581075</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.0005254847210538927</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>22.77702422581075</v>
+        <v>736.7167641813118</v>
       </c>
       <c r="E30" t="n">
-        <v>0.17</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0005254847210538927</v>
+        <v>0</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>736.7167641813118</v>
+        <v>14.17123841133722</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.02</v>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>9.152678157129605</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>14.17123841133722</v>
+        <v>6452.588852933619</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02</v>
+        <v>0.96</v>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.152678157129605</v>
+        <v>0.0546706787533466</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>6452.588852933619</v>
+        <v>303.6342554993155</v>
       </c>
       <c r="E33" t="n">
-        <v>0.96</v>
+        <v>0.65</v>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0546706787533466</v>
+        <v>1.278639935284393</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>303.6342554993155</v>
+        <v>493.0000417673714</v>
       </c>
       <c r="E34" t="n">
-        <v>0.65</v>
+        <v>0.87</v>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.278639935284393</v>
+        <v>17.4220899530211</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>493.0000417673714</v>
+        <v>1008.508613796855</v>
       </c>
       <c r="E35" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>17.4220899530211</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1008.508613796855</v>
+        <v>446.1608905425159</v>
       </c>
       <c r="E36" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>446.1608905425159</v>
-      </c>
-      <c r="E37" t="n">
         <v>0.74</v>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1571,9 +1662,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1589,9 +1677,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1607,9 +1692,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1625,9 +1707,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1643,9 +1722,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1661,9 +1737,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1698,9 +1771,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1718,9 +1788,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1738,9 +1805,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1758,9 +1822,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1778,9 +1839,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1798,9 +1856,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1818,9 +1873,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1838,9 +1890,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1858,9 +1907,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1878,9 +1924,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1898,9 +1941,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1918,9 +1958,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1938,9 +1975,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1958,9 +1992,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1978,9 +2009,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1998,9 +2026,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2018,9 +2043,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2038,9 +2060,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2058,9 +2077,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2078,9 +2094,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2098,9 +2111,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2118,9 +2128,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2138,9 +2145,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2158,9 +2162,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2178,9 +2179,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2198,9 +2196,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2218,9 +2213,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2238,9 +2230,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2258,9 +2247,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2278,9 +2264,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2298,9 +2281,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2318,9 +2298,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2338,9 +2315,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2358,9 +2332,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2378,9 +2349,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2398,9 +2366,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2418,9 +2383,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2438,9 +2400,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2458,9 +2417,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2478,9 +2434,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2498,9 +2451,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2518,9 +2468,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2538,9 +2485,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2558,9 +2502,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2578,9 +2519,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2598,9 +2536,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2618,9 +2553,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2638,9 +2570,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2658,9 +2587,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2678,9 +2604,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2701,9 +2624,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2724,9 +2644,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2747,9 +2664,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2770,9 +2684,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2792,9 +2703,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
